--- a/Finanzas_ETC88.xlsx
+++ b/Finanzas_ETC88.xlsx
@@ -155,9 +155,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -172,6 +169,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -870,7 +870,11 @@
       <c r="B21" s="4" t="n">
         <v>518381</v>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Estimado · suma de la hoja Resumen</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -901,15 +905,15 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas equipo (47 × $5,000 mensual)</t>
+          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>235000</v>
+        <v>70500</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Propuesta: $1,250/mes × 4 meses · sinceriza costo</t>
+          <t>[PROPUESTA] $500/mes · total $1,500–$2,000/persona · SIN CERRAR · rango agregado $70,500–$94,000</t>
         </is>
       </c>
     </row>
@@ -922,7 +926,11 @@
       <c r="B25" s="4" t="n">
         <v>144000</v>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Confirmado: $3,000/participante</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -935,7 +943,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Premio donado idealmente</t>
+          <t>[PROPUESTA] Meta a validar · premio donado idealmente</t>
         </is>
       </c>
     </row>
@@ -950,7 +958,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Responsabilidad de Directores (delegable)</t>
+          <t>[PROPUESTA] Responsabilidad de Directores (delegable)</t>
         </is>
       </c>
     </row>
@@ -965,37 +973,22 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Benchmark ETC 79 = $50K garaje</t>
+          <t>[PROPUESTA] Benchmark ETC 79 = $50K garaje</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>(-) Exención casa (ya descontada arriba)</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>0</v>
+          <t>(=) Faltante indicativo (cuota media)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>85731</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>$28,500 ahorro incluido en línea de casa</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>(=) Sobrante / (Brecha)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>67019</v>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Margen positivo si todo se cumple</t>
+          <t>INDICATIVO · cambia con la cuota final y la recaudación. Positivo = aún falta cubrir. Por eso la meta debe ser agresiva.</t>
         </is>
       </c>
     </row>
@@ -1024,34 +1017,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>RECAUDACIÓN — meta agresiva $260K</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>RECAUDACIÓN · meta propuesta $260,000 · [PROPUESTA] a validar</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Meta (RD$)</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -1068,7 +1061,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Por arrancar</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1078,7 +1071,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Premio donado · 1,200 boletos a $100 · cierre 2-ago</t>
+          <t>[PROPUESTA] Meta neta a validar · premio donado idealmente</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1086,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Por gestionar</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1103,7 +1096,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Delegable a Recaudación</t>
+          <t>[PROPUESTA] Delegable a Recaudación</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1111,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Por definir</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1128,7 +1121,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Benchmark ETC 79 = $50K garaje</t>
+          <t>[PROPUESTA] Benchmark ETC 79 = $50K garaje</t>
         </is>
       </c>
     </row>
@@ -1153,22 +1146,22 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Diferencia $300/p × 95 personas</t>
+          <t>Ahorro $300/persona × ~95 (incluye 48 part. estimados)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Aportes mensuales equipo (47 × $5K)</t>
+          <t>Aportes equipo (47 × $1,500–2,000)</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>235000</v>
+        <v>82250</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Por arrancar</t>
+          <t>PROPUESTA</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1178,14 +1171,14 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>$1,250/mes × 4 meses</t>
+          <t>[PROPUESTA] $500/mes · total $1,500–$2,000/persona · SIN CERRAR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Cuotas participantes (48 × $3K)</t>
+          <t>Cuotas participantes (48 × $3,000)</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -1193,7 +1186,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Por cobrar</t>
+          <t>Confirmado</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1214,7 +1207,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>637500</v>
+        <v>484750</v>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr"/>
@@ -1250,7 +1243,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>APORTES MENSUALES DEL EQUIPO · $1,250 × 4 meses</t>
+          <t>[PROPUESTA] APORTES DEL EQUIPO · $500/mes · total $1,500–$2,000/persona (SIN CERRAR)</t>
         </is>
       </c>
     </row>
@@ -1308,21 +1301,25 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1336,21 +1333,25 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1364,21 +1365,25 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1392,21 +1397,25 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1420,21 +1429,25 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1448,21 +1461,25 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1476,21 +1493,25 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1504,21 +1525,25 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1532,21 +1557,25 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1560,21 +1589,25 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1588,21 +1621,25 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1616,21 +1653,25 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1644,21 +1685,25 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1672,21 +1717,25 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1700,21 +1749,25 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1728,21 +1781,25 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1756,21 +1813,25 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1784,21 +1845,25 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1812,21 +1877,25 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1840,21 +1909,25 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1868,21 +1941,25 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1896,21 +1973,25 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1924,21 +2005,25 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1952,21 +2037,25 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1980,21 +2069,25 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2008,21 +2101,25 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2036,21 +2133,25 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2064,21 +2165,25 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2092,21 +2197,25 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2120,21 +2229,25 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2148,21 +2261,25 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2176,21 +2293,25 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2204,21 +2325,25 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2232,21 +2357,25 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2260,21 +2389,25 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2288,21 +2421,25 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2316,21 +2453,25 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2344,21 +2485,25 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2372,21 +2517,25 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2400,21 +2549,25 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2428,21 +2581,25 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2456,21 +2613,25 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2484,21 +2645,25 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2512,21 +2677,25 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2540,21 +2709,25 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2568,21 +2741,25 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2596,45 +2773,53 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>TOTAL OBJETIVO</t>
+          <t>TOTAL OBJETIVO (propuesta)</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="6" t="n">
-        <v>58750</v>
+        <v>23500</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>58750</v>
+        <v>23500</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>58750</v>
+        <v>23500</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>58750</v>
+        <v>23500</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>235000</v>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
+        <v>94000</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[PROPUESTA] </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2704,14 +2889,14 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>4. Recaudación lleva la meta agresiva ($260K). Estado se actualiza semanalmente.</t>
+          <t>4. Recaudación lleva la meta PROPUESTA (a validar). El estado se actualiza semanalmente.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>5. Pagos Equipo: aporte recomendado $1,250/mes × 4 meses por persona (sinceriza costos).</t>
+          <t>5. Pagos Equipo: cuota PROPUESTA de $500/mes (total $1,500–2,000/persona). SIN CERRAR — la decide la Dirección.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2941,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>• Equipo: 47 operativos + 48 participantes objetivo = 95 personas a la casa.</t>
+          <t>• Equipo: 47 operativos + 48 participantes (estimado) = 95 personas a la casa.</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2958,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>• Confirmar precio real de la casa 2026 (los $2,300 son del ETC 86) — llamar a Samuel Montilla.</t>
+          <t>• Cerrar el monto final de la cuota del equipo (propuesta $500/mes, total $1,500–2,000).</t>
         </is>
       </c>
     </row>
@@ -2969,39 +3154,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>MENÚ POR TIEMPO DE COMIDA · estructura sin precios (a llenar)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Día</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Tiempo</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Plato principal</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Acompañante</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Bebida</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Postre/Notas</t>
         </is>
@@ -3301,39 +3486,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>COCINA · LISTA DE COMPRAS (canasta · precios 2026)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Artículo</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Responsable / Donación</t>
         </is>
@@ -4097,39 +4282,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>MATERIALES Y LITÚRGICO (itemizado)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Artículo</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Notas / Momento</t>
         </is>
@@ -5011,39 +5196,39 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>MÚSICA · Cancionero + respaldo (la casa tiene sonido)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Artículo</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>P. Unit.</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -5159,7 +5344,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>FORMACIONES (5 sesiones · jun-ago)</t>
         </is>
@@ -5211,7 +5396,7 @@
       <c r="C4" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
@@ -5235,7 +5420,7 @@
       <c r="C5" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
@@ -5259,7 +5444,7 @@
       <c r="C6" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
@@ -5283,7 +5468,7 @@
       <c r="C7" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="4" t="n">
@@ -5307,7 +5492,7 @@
       <c r="C8" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
@@ -5328,16 +5513,16 @@
           <t>4-jun</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5379,7 +5564,7 @@
       <c r="C11" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="4" t="n">
@@ -5403,7 +5588,7 @@
       <c r="C12" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="4" t="n">

--- a/Finanzas_ETC88.xlsx
+++ b/Finanzas_ETC88.xlsx
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -593,221 +593,221 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Casa de retiro (con exención $2,000/p × 95 pers.)</t>
+          <t>Casa de retiro (con exención $2,000/p × 100 pers.)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>218500</v>
+        <v>200000</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>CON exención de la parroquia de Paul · 47 equipo + 48 part.</t>
+          <t>CON exención · 47 equipo + ~53 part. = 100 en la casa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Casa de retiro (sin exención $2,300/p)</t>
+          <t>Transporte (SPM→Higüey, equipo + participantes + clausura)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>218500</v>
+        <v>69000</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>218500</v>
+        <v>77500</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>251000</v>
+        <v>86000</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Si NO se consigue exención</t>
+          <t>3 cotizaciones a pedir (Metro, Transportando RD, DominicanBus)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Transporte (SPM→Higüey, equipo + participantes + clausura)</t>
+          <t>Cocina · Mercado (canasta)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>69000</v>
+        <v>59000</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>77500</v>
+        <v>62410</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>86000</v>
+        <v>65800</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>3 cotizaciones a pedir (Metro, Transportando RD, DominicanBus)</t>
+          <t>La casa INCLUYE gas; no se compra gasoil</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Cocina · Mercado (canasta)</t>
+          <t>Cocina · Meriendas / Correcaminos</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>59000</v>
+        <v>9000</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>62410</v>
+        <v>9756</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>65800</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>La casa INCLUYE gas; no se compra gasoil</t>
-        </is>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Cocina · Meriendas / Correcaminos</t>
+          <t>Cocina · Decoración / motivos comedor</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9756</v>
+        <v>10000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Foami, velas, flores, cajitas, hilo (ref. ETC 78)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Cocina · Decoración / motivos comedor</t>
+          <t>Materiales y Litúrgico (itemizado)</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>8000</v>
+        <v>80000</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10000</v>
+        <v>88500</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12000</v>
+        <v>95000</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Foami, velas, flores, cajitas, hilo (ref. ETC 78)</t>
+          <t>Peces + Biblias + Banderín + Rosarios + Cofre palancas + Vino + Ofrenda confesores</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Materiales y Litúrgico (itemizado)</t>
+          <t>Guías · Materiales del PG (libretas, sobres, alambre…)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>80000</v>
+        <v>14000</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>88500</v>
+        <v>17000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>95000</v>
+        <v>20000</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Peces + Biblias + Banderín + Rosarios + Cofre palancas + Vino + Ofrenda confesores</t>
+          <t>Libretas para participantes EN ESTE rubro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Guías · Materiales del PG (libretas, sobres, alambre…)</t>
+          <t>Música · Impresión cancionero + cables/respaldo</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>17000</v>
+        <v>4500</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Libretas para participantes EN ESTE rubro</t>
+          <t>La casa tiene sonido; solo respaldo</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Música · Impresión cancionero + cables/respaldo</t>
+          <t>Formaciones (5 sesiones · refrigerio + local)</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3000</v>
+        <v>13000</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4500</v>
+        <v>16315</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>La casa tiene sonido; solo respaldo</t>
-        </is>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Formaciones (5 sesiones · refrigerio + local)</t>
+          <t>Imprevistos 5%</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>13000</v>
+        <v>22000</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>16315</v>
+        <v>23900</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Imprevistos 5%</t>
+          <t>Casa SIN exención ($2,300/p × 100) — alternativa</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>22000</v>
+        <v>230000</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>23900</v>
+        <v>230000</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+        <v>230000</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Si NO se consigue exención: reemplaza la línea de casa (no se suma aquí)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr"/>
@@ -819,21 +819,21 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TOTAL ESTIMADO</t>
+          <t>TOTAL ESTIMADO (con exención)</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>485500</v>
+        <v>477000</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>518381</v>
+        <v>509881</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>559300</v>
+        <v>539800</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Base 518K; con exención ahorra ~$28K</t>
+          <t>Casa a 100 personas; precios ESTIMADOS a validar en F1</t>
         </is>
       </c>
     </row>
@@ -864,15 +864,15 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>(+) Costo estimado base</t>
+          <t>(+) Costo estimado base (con exención)</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>518381</v>
+        <v>509881</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Estimado · suma de la hoja Resumen</t>
+          <t>Estimado · suma de arriba; precios a validar en F1</t>
         </is>
       </c>
     </row>
@@ -894,101 +894,60 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>(=) Total a cubrir</t>
+          <t>(=) Total a cubrir = META de recaudación</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>541981</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
+        <v>533481</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>La meta NO es un número fijo: es este costo total.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
+          <t>(-) Cuotas participantes (~53 × $3,000)</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>70500</v>
+        <v>159000</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] $500/mes · total $1,500–$2,000/persona · SIN CERRAR · rango agregado $70,500–$94,000</t>
+          <t>Para completar 100 en la casa · confirmado $3,000/participante</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas participantes (48 × $3,000)</t>
+          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>144000</v>
+        <v>82250</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Confirmado: $3,000/participante</t>
+          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>(-) Rifa (Profondo #1 neto)</t>
+          <t>(=) BRECHA: rifa + venta de comida + donaciones</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>130000</v>
+        <v>292231</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] Meta a validar · premio donado idealmente</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>(-) Donaciones empresas/particulares</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>[PROPUESTA] Responsabilidad de Directores (delegable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>(-) Profondo #2 (venta comida/garaje)</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>[PROPUESTA] Benchmark ETC 79 = $50K garaje</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>(=) Faltante indicativo (cuota media)</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>85731</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>INDICATIVO · cambia con la cuota final y la recaudación. Positivo = aún falta cubrir. Por eso la meta debe ser agresiva.</t>
+          <t>Montos VARIABLES (lo que se recaude). Rifa = primera actividad. Donaciones = responsabilidad de Directores.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1019,7 +978,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>RECAUDACIÓN · meta propuesta $260,000 · [PROPUESTA] a validar</t>
+          <t>RECAUDACIÓN · la META = costo total $533,481 (cuotas + rifa/comida + donaciones)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +990,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Meta (RD$)</t>
+          <t>Monto (RD$)</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -1053,36 +1012,36 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Rifa (Profondo #1)</t>
+          <t>Cuotas participantes (~53 × $3,000)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>130000</v>
+        <v>159000</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>Confirmado</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Co-Dir + Recaudación</t>
+          <t>Cada misionero</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] Meta neta a validar · premio donado idealmente</t>
+          <t>Para completar 100 en la casa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Donaciones a empresas/particulares</t>
+          <t>Aportes equipo (47 × $1,500–2,000)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>50000</v>
+        <v>82250</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -1091,127 +1050,124 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>DIRECTORES (resp.)</t>
+          <t>Cada miembro</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] Delegable a Recaudación</t>
+          <t>[PROPUESTA] $500/mes · SIN CERRAR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Profondo #2 (venta de comida / garaje)</t>
+          <t>Exención casa (vía RNC parroquia Paul)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>Por gestionar</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Equipo completo</t>
+          <t>Co-Dir + Padre Paul</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] Benchmark ETC 79 = $50K garaje</t>
+          <t>Ahorro $300/persona × 100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Exención casa (vía RNC parroquia Paul)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>28500</v>
-      </c>
+          <t>Rifa (Profondo #1)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Por gestionar</t>
+          <t>VARIABLE</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Co-Dir + Padre Paul</t>
+          <t>Co-Dir + Recaudación</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Ahorro $300/persona × ~95 (incluye 48 part. estimados)</t>
+          <t>Primera actividad · lo que se recaude</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Aportes equipo (47 × $1,500–2,000)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>82250</v>
-      </c>
+          <t>Venta de comida (Profondo #2)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>PROPUESTA</t>
+          <t>VARIABLE</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cada miembro</t>
+          <t>Equipo completo</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] $500/mes · total $1,500–$2,000/persona · SIN CERRAR</t>
+          <t>Lo que se recaude</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Cuotas participantes (48 × $3,000)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>144000</v>
-      </c>
+          <t>Donaciones empresas/particulares</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>VARIABLE</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Cada misionero</t>
+          <t>DIRECTORES (resp.)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Misionero gestiona su invitado</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL RECAUDACIÓN OBJETIVO</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>484750</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
+          <t>Lo que se recaude · delegable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <f> BRECHA a cubrir con rifa + comida + donaciones</f>
+        <v/>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>292231</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Costo total − cuotas: esto es lo que la recaudación variable debe levantar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1644,7 +1600,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Fabelle maciel fabian bello</t>
+          <t>Fabelly Maciel Fabian Bello</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1676,7 +1632,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Guido Mardonado</t>
+          <t>Guido Maldonado</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2835,7 +2791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2889,109 +2845,116 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>4. Recaudación lleva la meta PROPUESTA (a validar). El estado se actualiza semanalmente.</t>
+          <t>4. Recaudación: la META = el costo total. Se cubre con cuotas (participantes + equipo) +</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
+          <t xml:space="preserve">   rifa + venta de comida + donaciones (montos VARIABLES, lo que se recaude).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
           <t>5. Pagos Equipo: cuota PROPUESTA de $500/mes (total $1,500–2,000/persona). SIN CERRAR — la decide la Dirección.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>CONTEXTO CRÍTICO:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>• Arrancamos en NEGATIVO: $23,600 (10% reserva casa pagada por Juan Manuel ya devuelto al Consejo).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Es la PRIMERA deuda a cubrir con la recaudación.</t>
+          <t>• Arrancamos en NEGATIVO: $23,600 (10% reserva casa pagada por Juan Manuel ya devuelto al Consejo).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>• La casa INCLUYE gas y limpieza (no se compra). Con exención: $2,000/p; sin exención: $2,300/p.</t>
+          <t xml:space="preserve">  Es la PRIMERA deuda a cubrir con la recaudación.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>• Casa tiene sonido (música solo lleva respaldo).</t>
+          <t>• La casa INCLUYE gas y limpieza (no se compra). Con exención: $2,000/p; sin exención: $2,300/p.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>• Equipo: 47 operativos + 48 participantes (estimado) = 95 personas a la casa.</t>
+          <t>• Casa tiene sonido (música solo lleva respaldo).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr"/>
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>• Piso de personas: completar 100 en la casa (≈47 operativos + ~53 participantes).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>PENDIENTES PARA CERRAR EL PRESUPUESTO:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>• Cerrar el monto final de la cuota del equipo (propuesta $500/mes, total $1,500–2,000).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>• Gestionar exención con el Padre Paul (impacto $28,500).</t>
+          <t>• Cerrar el monto final de la cuota del equipo (propuesta $500/mes, total $1,500–2,000).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>• Cotizar transporte (3 empresas).</t>
+          <t>• Gestionar exención con el Padre Paul (impacto ~$30,000 a 100 personas).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>• Banderín: diseño + cotización (~$5K estimado).</t>
+          <t>• Cotizar transporte (3 empresas) · fijar fecha límite (también biblias y peces).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>• Confirmar # final de participantes (afecta peces, biblias, comida).</t>
+          <t>• Banderín: diseño + cotización.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>• Confirmar el conteo final para completar 100 en la casa (afecta peces, biblias, comida).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>• Donaciones en especie: arroz, habichuelas, aceite (el ETC 79 los consiguió donados).</t>
         </is>
@@ -3059,17 +3022,17 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2300</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>218500</v>
+        <v>230000</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Tarifa estándar</t>
+          <t>Tarifa estándar · piso de 100 personas</t>
         </is>
       </c>
     </row>
@@ -3080,17 +3043,17 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AHORRO: $28,500 · diferencia $300/persona</t>
+          <t>AHORRO $30,000 · diferencia $300/persona</t>
         </is>
       </c>
     </row>
@@ -3114,17 +3077,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Saldo pendiente con exención</t>
+          <t>Saldo con exención tras la deuda</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="4" t="n">
-        <v>166400</v>
+        <v>176400</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>190,000 - 23,600 = 166,400</t>
+          <t>200,000 - 23,600</t>
         </is>
       </c>
     </row>

--- a/Finanzas_ETC88.xlsx
+++ b/Finanzas_ETC88.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transporte" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recaudación" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagos Equipo" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usar" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camisetas" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usar" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +58,11 @@
       <b val="1"/>
       <color rgb="00B25028"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B25028"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -181,6 +187,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -774,178 +781,220 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Imprevistos 5%</t>
+          <t>Camisetas del equipo (~56 × est.)</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>22000</v>
+        <v>19600</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>23900</v>
+        <v>22400</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+        <v>28000</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Tallas PARCIALES (ver pestaña Camisetas); faltan invitados pendientes + Paul, Frank y la Sor. Mockup tras el Design System.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Avanzada jueves 3-sep (porción casa + 3 comidas del equipo que adelanta)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRMAR con la casa la tarifa de noche/día extra; depende de cuántos adelantan (cocina). Desayuno + almuerzo + cena de ese día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Imprevistos 5%</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>23900</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Casa SIN exención ($2,300/p × 100) — alternativa</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B16" s="4" t="n">
         <v>230000</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C16" s="4" t="n">
         <v>230000</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D16" s="4" t="n">
         <v>230000</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Si NO se consigue exención: reemplaza la línea de casa (no se suma aquí)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TOTAL ESTIMADO (con exención)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>477000</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>509881</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>539800</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="B18" s="6" t="n">
+        <v>511600</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>552281</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>591800</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Casa a 100 personas; precios ESTIMADOS a validar en F1</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>BRECHA Y RECAUDACIÓN</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Notas</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>(+) Costo estimado base (con exención)</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>509881</v>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Estimado · suma de arriba; precios a validar en F1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>(+) Deuda inicial al Consejo (10% casa)</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>23600</v>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Juan Manuel pagó 5-mar; ya devuelto. Arrancamos en NEGATIVO.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>(=) Total a cubrir = META de recaudación</t>
+          <t>(+) Costo estimado base (con exención)</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>533481</v>
+        <v>552281</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>La meta NO es un número fijo: es este costo total.</t>
+          <t>Estimado · suma de arriba; precios a validar en F1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas participantes (~53 × $3,000)</t>
+          <t>(+) Deuda inicial al Consejo (10% casa)</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>159000</v>
+        <v>23600</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Para completar 100 en la casa · confirmado $3,000/participante</t>
+          <t>Juan Manuel pagó 5-mar; ya devuelto. Arrancamos en NEGATIVO.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
+          <t>(=) Total a cubrir = META de recaudación</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>82250</v>
+        <v>575881</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
+          <t>La meta NO es un número fijo: es este costo total.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>(-) Cuotas participantes (~53 × $3,000)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>159000</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Para completar 100 en la casa · confirmado $3,000/participante</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>82250</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>(=) BRECHA: rifa + venta de comida + donaciones</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>292231</v>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B28" s="4" t="n">
+        <v>334631</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Montos VARIABLES (lo que se recaude). Rifa = primera actividad. Donaciones = responsabilidad de Directores.</t>
         </is>
@@ -978,7 +1027,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>RECAUDACIÓN · la META = costo total $533,481 (cuotas + rifa/comida + donaciones)</t>
+          <t>RECAUDACIÓN · la META = costo total $575,881 (cuotas + rifa/comida + donaciones)</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1208,7 @@
         <v/>
       </c>
       <c r="B10" s="4" t="n">
-        <v>292231</v>
+        <v>334631</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
@@ -2791,6 +2840,348 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>CAMISETAS DEL EQUIPO · tallas (parcial) — mockup tras el Design System</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Talla</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>XXL</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CON talla</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>de 52 del equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>FALTAN talla</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>pedir antes de imprimir</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>A QUIÉNES FALTA LA TALLA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Frank Morales</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>asesores</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Johanny García</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>asesores_cocina</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Mary "Peta" Morales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>asesores_cocina</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Leticia González</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Marleny</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sandrita</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>asesores_diocesanos</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Padre Paul Ramírez</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>asesores_espirituales</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sor Angelina Lebrón</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>asesores_espirituales</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Olanlly</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Daylin</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>musica</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2798,163 +3189,163 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>FINANZAS ETC 88 — HOJA VIVA · v8 · 2-jun-2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr"/>
+      <c r="A2" s="19" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Cómo se usa:</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>1. La pestaña Resumen es la foto ejecutiva. Lee primero.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2. Las pestañas por área (Casa, Cocina-Compras, Materiales, Guías, Música, Formaciones, Transporte)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">   son lo que cada coordinador entrega y refina en F1 (14-jun). Precios son ESTIMADOS a validar.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>3. Menú es estructura sin precios; cocina lo refina y de ahí salen las cantidades de Cocina-Compras.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>4. Recaudación: la META = el costo total. Se cubre con cuotas (participantes + equipo) +</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">   rifa + venta de comida + donaciones (montos VARIABLES, lo que se recaude).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>5. Pagos Equipo: cuota PROPUESTA de $500/mes (total $1,500–2,000/persona). SIN CERRAR — la decide la Dirección.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr"/>
+      <c r="A11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>CONTEXTO CRÍTICO:</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>• Arrancamos en NEGATIVO: $23,600 (10% reserva casa pagada por Juan Manuel ya devuelto al Consejo).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Es la PRIMERA deuda a cubrir con la recaudación.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>• La casa INCLUYE gas y limpieza (no se compra). Con exención: $2,000/p; sin exención: $2,300/p.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>• Casa tiene sonido (música solo lleva respaldo).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>• Piso de personas: completar 100 en la casa (≈47 operativos + ~53 participantes).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr"/>
+      <c r="A18" s="19" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>PENDIENTES PARA CERRAR EL PRESUPUESTO:</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>• Cerrar el monto final de la cuota del equipo (propuesta $500/mes, total $1,500–2,000).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>• Gestionar exención con el Padre Paul (impacto ~$30,000 a 100 personas).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>• Cotizar transporte (3 empresas) · fijar fecha límite (también biblias y peces).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>• Banderín: diseño + cotización.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>• Confirmar el conteo final para completar 100 en la casa (afecta peces, biblias, comida).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>• Donaciones en especie: arroz, habichuelas, aceite (el ETC 79 los consiguió donados).</t>
         </is>

--- a/Finanzas_ETC88.xlsx
+++ b/Finanzas_ETC88.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -764,7 +764,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Formaciones (5 sesiones · refrigerio + local)</t>
+          <t>Formaciones F1–F5 (5 sesiones · refrigerio + local)</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -781,220 +781,283 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Camisetas del equipo (~56 × est.)</t>
+          <t>Convivencia del equipo (22-ago · día completo)</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>19600</v>
+        <v>8000</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>22400</v>
+        <v>12000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>28000</v>
+        <v>18000</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Tallas PARCIALES (ver pestaña Camisetas); faltan invitados pendientes + Paul, Frank y la Sor. Mockup tras el Design System.</t>
+          <t>Miniretiro; confirmar si incluye almuerzo del equipo y local</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Avanzada jueves 3-sep (porción casa + 3 comidas del equipo que adelanta)</t>
+          <t>Ensayo General (23-ago · INCLUYE el almuerzo del equipo)</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="C14" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>24000</v>
-      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>CONFIRMAR con la casa la tarifa de noche/día extra; depende de cuántos adelantan (cocina). Desayuno + almuerzo + cena de ese día.</t>
+          <t>Almuerzo ~52 personas + refrigerio + local</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Imprevistos 5%</t>
+          <t>Bienvenida post-ETC (9-sep · bizcocho)</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>22000</v>
+        <v>2000</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>23900</v>
+        <v>3000</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
+        <v>4500</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Bizcocho de bienvenida de los nuevos (1ra reunión post-retiro)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Camisetas del equipo (~56 × est.)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>19600</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>22400</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Tallas PARCIALES (ver pestaña Camisetas); faltan invitados pendientes + Paul, Frank y la Sor. Mockup tras el Design System.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Avanzada jueves 3-sep (porción casa + 3 comidas del equipo que adelanta)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRMAR con la casa la tarifa de noche/día extra; depende de cuántos adelantan (cocina). Desayuno + almuerzo + cena de ese día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Imprevistos 5%</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>23900</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Casa SIN exención ($2,300/p × 100) — alternativa</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B19" s="4" t="n">
         <v>230000</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C19" s="4" t="n">
         <v>230000</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D19" s="4" t="n">
         <v>230000</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Si NO se consigue exención: reemplaza la línea de casa (no se suma aquí)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>TOTAL ESTIMADO (con exención)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>511600</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>552281</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>591800</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="B21" s="6" t="n">
+        <v>533600</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>583281</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>634300</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Casa a 100 personas; precios ESTIMADOS a validar en F1</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>BRECHA Y RECAUDACIÓN</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Notas</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>(+) Costo estimado base (con exención)</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>552281</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Estimado · suma de arriba; precios a validar en F1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>(+) Deuda inicial al Consejo (10% casa)</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>23600</v>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Juan Manuel pagó 5-mar; ya devuelto. Arrancamos en NEGATIVO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>(=) Total a cubrir = META de recaudación</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>575881</v>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>La meta NO es un número fijo: es este costo total.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas participantes (~53 × $3,000)</t>
+          <t>(+) Costo estimado base (con exención)</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>159000</v>
+        <v>583281</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Para completar 100 en la casa · confirmado $3,000/participante</t>
+          <t>Estimado · suma de arriba; precios a validar en F1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
+          <t>(+) Deuda inicial al Consejo (10% casa)</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>82250</v>
+        <v>23600</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
+          <t>Juan Manuel pagó 5-mar; ya devuelto. Arrancamos en NEGATIVO.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>(=) Total a cubrir = META de recaudación</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>606881</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>La meta NO es un número fijo: es este costo total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>(-) Cuotas participantes (~53 × $3,000)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>159000</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Para completar 100 en la casa · confirmado $3,000/participante</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>82250</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>(=) BRECHA: rifa + venta de comida + donaciones</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>334631</v>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="B31" s="4" t="n">
+        <v>365631</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Montos VARIABLES (lo que se recaude). Rifa = primera actividad. Donaciones = responsabilidad de Directores.</t>
         </is>
@@ -1027,7 +1090,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>RECAUDACIÓN · la META = costo total $575,881 (cuotas + rifa/comida + donaciones)</t>
+          <t>RECAUDACIÓN · la META = costo total $606,881 (cuotas + rifa/comida + donaciones)</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1271,7 @@
         <v/>
       </c>
       <c r="B10" s="4" t="n">
-        <v>334631</v>
+        <v>365631</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
@@ -3018,7 +3081,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Mary "Peta" Morales</t>
+          <t>Mary "Petra" Morales</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -5686,7 +5749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5883,7 +5946,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Convivencia (miniretiro)</t>
+          <t>Convivencia (miniretiro · día completo)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -5892,22 +5955,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>2000</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Ensayo General</t>
+          <t>Ensayo General (incluye almuerzo del equipo)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5916,7 +5979,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>0</v>
@@ -5925,7 +5988,7 @@
         <v>1000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="12">
@@ -5952,18 +6015,42 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Bienvenida post-ETC (bizcocho)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>9-sep</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TOTAL FORMACIONES</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
-        <v>26100</v>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="n">
+        <v>47600</v>
       </c>
     </row>
   </sheetData>

--- a/Finanzas_ETC88.xlsx
+++ b/Finanzas_ETC88.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -976,7 +976,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>(+) Costo estimado base (con exención)</t>
+          <t>(=) Costo total a cubrir = META de recaudación</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
@@ -984,80 +984,63 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Estimado · suma de arriba; precios a validar en F1</t>
+          <t>Incluye la casa completa; precios ESTIMADOS a validar en F1. La meta NO es fija: es el costo.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>(+) Deuda inicial al Consejo (10% casa)</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>23600</v>
-      </c>
+          <t xml:space="preserve">    · de la casa ($200,000), $23,600 se deben al Consejo</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Juan Manuel pagó 5-mar; ya devuelto. Arrancamos en NEGATIVO.</t>
+          <t>Reserva (10%) ya pagada por JM; es la PRIMERA salida. Arrancamos en negativo (NO se suma: ya está dentro de la casa).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>(=) Total a cubrir = META de recaudación</t>
+          <t>(-) Cuotas participantes (~53 × $3,000)</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>606881</v>
+        <v>159000</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>La meta NO es un número fijo: es este costo total.</t>
+          <t>Para completar 100 en la casa · confirmado $3,000/participante</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas participantes (~53 × $3,000)</t>
+          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>159000</v>
+        <v>82250</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Para completar 100 en la casa · confirmado $3,000/participante</t>
+          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
+          <t>(=) BRECHA: rifa + venta de comida + donaciones</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>82250</v>
+        <v>342031</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>(=) BRECHA: rifa + venta de comida + donaciones</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>365631</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Montos VARIABLES (lo que se recaude). Rifa = primera actividad. Donaciones = responsabilidad de Directores.</t>
         </is>
@@ -1090,7 +1073,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>RECAUDACIÓN · la META = costo total $606,881 (cuotas + rifa/comida + donaciones)</t>
+          <t>RECAUDACIÓN · la META = costo total $583,281 (cuotas + rifa/comida + donaciones)</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1254,7 @@
         <v/>
       </c>
       <c r="B10" s="4" t="n">
-        <v>365631</v>
+        <v>342031</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>

--- a/Finanzas_ETC88.xlsx
+++ b/Finanzas_ETC88.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>CON exención · 47 equipo + ~53 part. = 100 en la casa</t>
+          <t>CON exención · 48 equipo + ~52 part. = 100 en la casa</t>
         </is>
       </c>
     </row>
@@ -1004,11 +1004,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas participantes (~53 × $3,000)</t>
+          <t>(-) Cuotas participantes (~52 × $3,000)</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>159000</v>
+        <v>156000</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
@@ -1019,15 +1019,15 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>(-) Cuotas equipo (47 × $1,500–2,000)</t>
+          <t>(-) Cuotas equipo (48 × $1,500–2,000)</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>82250</v>
+        <v>84000</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $70,500–$94,000</t>
+          <t>[PROPUESTA] $500/mes · SIN CERRAR · rango $72,000–$96,000</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>342031</v>
+        <v>343281</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -1107,11 +1107,11 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cuotas participantes (~53 × $3,000)</t>
+          <t>Cuotas participantes (~52 × $3,000)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>159000</v>
+        <v>156000</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -1132,11 +1132,11 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Aportes equipo (47 × $1,500–2,000)</t>
+          <t>Aportes equipo (48 × $1,500–2,000)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>82250</v>
+        <v>84000</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v/>
       </c>
       <c r="B10" s="4" t="n">
-        <v>342031</v>
+        <v>343281</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1983,7 +1983,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Risaira Santana Rosario</t>
+          <t>Randolph Joseph</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Risairi Santana Rosario</t>
+          <t>Risaira Santana Rosario</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Roberto Figueroa</t>
+          <t>Risairi Santana Rosario</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Tommy Nova Nolasco</t>
+          <t>Roberto Figueroa</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Wirna Miguelina Stapleton Pilier</t>
+          <t>Tommy Nova Nolasco</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2143,12 +2143,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Jean Carlo De la Cruz Mendez</t>
+          <t>Wirna Miguelina Stapleton Pilier</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>directores</t>
+          <t>cocina</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -2175,7 +2175,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Juan Manuel de la Cruz Méndez</t>
+          <t>Jean Carlo De la Cruz Mendez</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2207,12 +2207,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Camila Fernández Hazim</t>
+          <t>Juan Manuel de la Cruz Méndez</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>guias</t>
+          <t>directores</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
@@ -2239,7 +2239,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Darianny Rodriguez Belliard</t>
+          <t>Camila Fernández Hazim</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Fernando Cordero</t>
+          <t>Darianny Rodriguez Belliard</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Franklin De Jesús Silverio Delgadillo</t>
+          <t>Fernando Cordero</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2335,7 +2335,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Ivanna Marien Mercedes Sosa</t>
+          <t>Franklin De Jesús Silverio Delgadillo</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Jhonnalia Franchesca Silvestre Guzmán</t>
+          <t>Ivanna Marien Mercedes Sosa</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Jonathan Andres Medina Mota</t>
+          <t>Jhonnalia Franchesca Silvestre Guzmán</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Juan Pablo Argüello Alzate</t>
+          <t>Jonathan Andres Medina Mota</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Luisa Maria Fiorentino Brugal</t>
+          <t>Juan Pablo Argüello Alzate</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2495,7 +2495,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Oliver Rafael De León Ramírez</t>
+          <t>Luisa Maria Fiorentino Brugal</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Priscilla Hidalgo Pou</t>
+          <t>Oliver Rafael De León Ramírez</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Victoria Lorenzo Rivera</t>
+          <t>Priscilla Hidalgo Pou</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Wilka María Reyes Mota</t>
+          <t>Victoria Lorenzo Rivera</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2623,7 +2623,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Yelaxni Mota</t>
+          <t>Wilka María Reyes Mota</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2655,12 +2655,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Daylin</t>
+          <t>Yelaxni Mota</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>musica</t>
+          <t>guias</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -2687,7 +2687,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Dorian Elina Rodriguez Belliard</t>
+          <t>Daylin</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Ismarie Sthepanie Constanzo Ramos</t>
+          <t>Dorian Elina Rodriguez Belliard</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2751,7 +2751,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>José Ángel Tusen Russo</t>
+          <t>Ismarie Sthepanie Constanzo Ramos</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Leober Carrion Soriano</t>
+          <t>José Ángel Tusen Russo</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Mary Carmen Ramírez Vásquez</t>
+          <t>Leober Carrion Soriano</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2844,29 +2844,61 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Mary Carmen Ramírez Vásquez</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>musica</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>[PROPUESTA] sin cerrar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>TOTAL OBJETIVO (propuesta)</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr"/>
-      <c r="C52" s="6" t="n">
-        <v>23500</v>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>23500</v>
-      </c>
-      <c r="E52" s="6" t="n">
-        <v>23500</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>23500</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>94000</v>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>96000</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">[PROPUESTA] </t>
         </is>
@@ -2886,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2984,7 +3016,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>de 52 del equipo</t>
+          <t>de 53 del equipo</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3027,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -3200,15 +3232,32 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>Randolph Joseph</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>cocina</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>sin formulario</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>Daylin</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>musica</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>sin formulario</t>
         </is>

--- a/Finanzas_ETC88.xlsx
+++ b/Finanzas_ETC88.xlsx
@@ -1887,7 +1887,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Olanlly</t>
+          <t>Marian Olanlly Ortiz Carrasco</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2918,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
     </row>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
     </row>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Olanlly</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3215,49 +3215,15 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Daylin</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>cocina</t>
+          <t>musica</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>sin formulario</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Randolph Joseph</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>cocina</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>sin formulario</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Daylin</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>musica</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>sin formulario</t>
         </is>
